--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="273">
   <si>
     <t>Backlog das Sprints — Sistema de Pesquisa Eleitoral</t>
   </si>
@@ -833,6 +833,12 @@
   </si>
   <si>
     <t>Homologação assistida com o Administrador montando um formulário real</t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>Em Andamento</t>
   </si>
 </sst>
 </file>
@@ -15016,7 +15022,7 @@
         <v>2.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>57</v>
@@ -15053,7 +15059,7 @@
         <v>5.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>68</v>
@@ -15090,7 +15096,7 @@
         <v>5.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>77</v>
@@ -15127,7 +15133,7 @@
         <v>3.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>90</v>
@@ -15164,7 +15170,7 @@
         <v>5.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>99</v>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -15170,7 +15170,7 @@
         <v>5.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>99</v>
@@ -16547,7 +16547,7 @@
         <v>5.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="4"/>
@@ -16575,7 +16575,7 @@
         <v>2.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="4"/>
@@ -16603,7 +16603,7 @@
         <v>3.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="4"/>
@@ -16631,7 +16631,7 @@
         <v>5.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="4"/>
@@ -16659,7 +16659,7 @@
         <v>5.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>92</v>
@@ -16689,7 +16689,7 @@
         <v>2.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>100</v>
@@ -16719,7 +16719,7 @@
         <v>2.0</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="4"/>
@@ -16747,7 +16747,7 @@
         <v>3.0</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="4"/>
@@ -16775,7 +16775,7 @@
         <v>5.0</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="4"/>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -17990,7 +17990,7 @@
         <v>3.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="4"/>
@@ -18015,7 +18015,7 @@
         <v>5.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="4"/>
@@ -18040,7 +18040,7 @@
         <v>8.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>66</v>
@@ -18067,7 +18067,7 @@
         <v>3.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="4"/>
@@ -18092,7 +18092,7 @@
         <v>2.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="4"/>
@@ -18117,7 +18117,7 @@
         <v>3.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="4"/>
@@ -18142,7 +18142,7 @@
         <v>8.0</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="4"/>
@@ -18167,7 +18167,7 @@
         <v>2.0</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>91</v>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -19394,7 +19394,7 @@
         <v>8.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>134</v>
@@ -19423,7 +19423,7 @@
         <v>3.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="4"/>
@@ -19450,7 +19450,7 @@
         <v>3.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="4"/>
@@ -19477,7 +19477,7 @@
         <v>5.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="4"/>
@@ -19504,7 +19504,7 @@
         <v>3.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="4"/>
@@ -19531,7 +19531,7 @@
         <v>3.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="4"/>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -20728,7 +20728,7 @@
         <v>5.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>153</v>
@@ -20755,7 +20755,7 @@
         <v>5.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>158</v>
@@ -20782,7 +20782,7 @@
         <v>3.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>164</v>
@@ -20809,7 +20809,7 @@
         <v>8.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="4"/>
@@ -20834,7 +20834,7 @@
         <v>5.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="4"/>
@@ -20859,7 +20859,7 @@
         <v>5.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="4"/>
@@ -20884,7 +20884,7 @@
         <v>5.0</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>185</v>
@@ -20911,7 +20911,7 @@
         <v>3.0</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="4"/>
@@ -20936,7 +20936,7 @@
         <v>2.0</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="4"/>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -22118,7 +22118,7 @@
         <v>8.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>174</v>
@@ -22144,7 +22144,7 @@
         <v>5.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>178</v>
@@ -22170,7 +22170,7 @@
         <v>2.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12"/>
     </row>
@@ -22194,7 +22194,7 @@
         <v>5.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>189</v>
@@ -22220,7 +22220,7 @@
         <v>2.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12"/>
     </row>
@@ -22244,7 +22244,7 @@
         <v>5.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12"/>
     </row>
@@ -22268,7 +22268,7 @@
         <v>8.0</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>201</v>
@@ -22294,7 +22294,7 @@
         <v>3.0</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>206</v>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -23474,7 +23474,7 @@
         <v>8.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12"/>
     </row>
@@ -23498,7 +23498,7 @@
         <v>5.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12"/>
     </row>
@@ -23522,7 +23522,7 @@
         <v>5.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>212</v>
@@ -23548,7 +23548,7 @@
         <v>3.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12"/>
     </row>
@@ -23572,7 +23572,7 @@
         <v>5.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12"/>
     </row>
@@ -23596,7 +23596,7 @@
         <v>8.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12"/>
     </row>
@@ -23620,7 +23620,7 @@
         <v>3.0</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H14" s="12"/>
     </row>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -24826,7 +24826,7 @@
         <v>5.0</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>226</v>
@@ -24856,7 +24856,7 @@
         <v>5.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="4"/>
@@ -24884,7 +24884,7 @@
         <v>8.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>231</v>
@@ -24914,7 +24914,7 @@
         <v>5.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>234</v>
@@ -24944,7 +24944,7 @@
         <v>5.0</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>237</v>
@@ -24974,7 +24974,7 @@
         <v>2.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="4"/>

--- a/docs/backlog-sprints-pesquisa-eleitoral.xlsx
+++ b/docs/backlog-sprints-pesquisa-eleitoral.xlsx
@@ -2721,7 +2721,7 @@
         <v>5.0</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>246</v>
@@ -2749,7 +2749,7 @@
         <v>3.0</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H9" s="22"/>
       <c r="I9" s="19"/>
@@ -2775,7 +2775,7 @@
         <v>3.0</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="19"/>
@@ -2801,7 +2801,7 @@
         <v>3.0</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="H11" s="22"/>
       <c r="I11" s="19"/>
@@ -2827,7 +2827,7 @@
         <v>5.0</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H12" s="22" t="s">
         <v>255</v>
@@ -2855,7 +2855,7 @@
         <v>3.0</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>258</v>
@@ -2883,7 +2883,7 @@
         <v>5.0</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="H14" s="22" t="s">
         <v>261</v>
@@ -2911,7 +2911,7 @@
         <v>5.0</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="H15" s="22" t="s">
         <v>264</v>
@@ -2965,7 +2965,7 @@
         <v>5.0</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>54</v>
+        <v>271</v>
       </c>
       <c r="H17" s="22"/>
       <c r="I17" s="19"/>
